--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260805.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260805.xlsx
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>157,499</t>
+          <t>104,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,392,000</t>
+          <t>157,499</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>202608WTEQ6F</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>1,392,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>202608WTEQ6F</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>104,000</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,907,000</t>
+          <t>387,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>387,000</t>
+          <t>1,907,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,353,000</t>
+          <t>5,888,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,888,000</t>
+          <t>3,353,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,434,384</t>
+          <t>3,621,981</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,621,981</t>
+          <t>1,434,384</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>4,634,578</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>4,634,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,233,076</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,233,076</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>5,160,956</t>
+          <t>188,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>188,000</t>
+          <t>5,160,956</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>97,000</t>
+          <t>302,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>120,000</t>
+          <t>1,623,400</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>302,000</t>
+          <t>837,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,623,400</t>
+          <t>120,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>837,000</t>
+          <t>97,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>332,000</t>
+          <t>236,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>236,000</t>
+          <t>405,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>405,000</t>
+          <t>332,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>345,000</t>
+          <t>177,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2354</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>鴻準</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>1,829,000</t>
+          <t>68,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>345,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>鴻準</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>68,538</t>
+          <t>1,829,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>185,000</t>
+          <t>264,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>264,000</t>
+          <t>707,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>163,000</t>
+          <t>185,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>707,000</t>
+          <t>163,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>新唐</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>74,000</t>
+          <t>349,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>新唐</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>349,000</t>
+          <t>74,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
